--- a/source/8、绩效异常岗位/7、扫描岗/扫描岗-6月.xlsx
+++ b/source/8、绩效异常岗位/7、扫描岗/扫描岗-6月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="59">
   <si>
     <t>数据日期</t>
   </si>
@@ -64,21 +64,12 @@
     <t>邢邯</t>
   </si>
   <si>
-    <t>74.3</t>
-  </si>
-  <si>
     <t>肃宁</t>
   </si>
   <si>
-    <t>76.9</t>
-  </si>
-  <si>
     <t>石家庄</t>
   </si>
   <si>
-    <t>69.2</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -88,90 +79,60 @@
     <t>柳州</t>
   </si>
   <si>
-    <t>68.8</t>
-  </si>
-  <si>
     <t>贵州区</t>
   </si>
   <si>
     <t>贵阳</t>
   </si>
   <si>
-    <t>144.8</t>
-  </si>
-  <si>
     <t>黑龙江区</t>
   </si>
   <si>
     <t>哈尔滨</t>
   </si>
   <si>
-    <t>73</t>
-  </si>
-  <si>
     <t>湖南区</t>
   </si>
   <si>
     <t>衡阳</t>
   </si>
   <si>
-    <t>84.8</t>
-  </si>
-  <si>
     <t>湖北区</t>
   </si>
   <si>
     <t>武汉</t>
   </si>
   <si>
-    <t>95.7</t>
-  </si>
-  <si>
     <t>山西区</t>
   </si>
   <si>
     <t>太原</t>
   </si>
   <si>
-    <t>169.2</t>
-  </si>
-  <si>
     <t>辽宁区</t>
   </si>
   <si>
     <t>盘锦</t>
   </si>
   <si>
-    <t>76.1</t>
-  </si>
-  <si>
     <t>江苏区</t>
   </si>
   <si>
     <t>南通</t>
   </si>
   <si>
-    <t>90.3</t>
-  </si>
-  <si>
     <t>浙北区</t>
   </si>
   <si>
     <t>杭州</t>
   </si>
   <si>
-    <t>97.5</t>
-  </si>
-  <si>
     <t>陕西区</t>
   </si>
   <si>
     <t>西安</t>
   </si>
   <si>
-    <t>107.1</t>
-  </si>
-  <si>
     <t>宁夏区</t>
   </si>
   <si>
@@ -184,46 +145,67 @@
     <t>义乌</t>
   </si>
   <si>
-    <t>117.3</t>
-  </si>
-  <si>
     <t>长沙</t>
   </si>
   <si>
-    <t>111.5</t>
-  </si>
-  <si>
     <t>广东区</t>
   </si>
   <si>
     <t>佛山</t>
   </si>
   <si>
-    <t>107.6</t>
-  </si>
-  <si>
     <t>山东区</t>
   </si>
   <si>
     <t>济南</t>
   </si>
   <si>
-    <t>103.8</t>
-  </si>
-  <si>
     <t>广州</t>
   </si>
   <si>
-    <t>125.4</t>
-  </si>
-  <si>
     <t>安徽区</t>
   </si>
   <si>
     <t>合肥</t>
   </si>
   <si>
-    <t>117.4</t>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>南京</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>荆州</t>
+  </si>
+  <si>
+    <t>苏州</t>
+  </si>
+  <si>
+    <t>临海</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>甘肃区</t>
+  </si>
+  <si>
+    <t>兰州</t>
+  </si>
+  <si>
+    <t>长治</t>
+  </si>
+  <si>
+    <t>安庆</t>
+  </si>
+  <si>
+    <t>深圳</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
   </si>
 </sst>
 </file>
@@ -1154,7 +1136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1193,8 +1175,8 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
+      <c r="D2">
+        <v>74.3</v>
       </c>
       <c r="E2">
         <v>110.2</v>
@@ -1217,10 +1199,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>76.9</v>
       </c>
       <c r="E3">
         <v>111.6</v>
@@ -1243,10 +1225,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>69.2</v>
       </c>
       <c r="E4">
         <v>94.6</v>
@@ -1255,10 +1237,10 @@
         <v>36.6</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1266,13 +1248,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>68.8</v>
       </c>
       <c r="E5">
         <v>89.1</v>
@@ -1281,10 +1263,10 @@
         <v>29.4</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1292,13 +1274,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>144.8</v>
       </c>
       <c r="E6">
         <v>186.4</v>
@@ -1318,13 +1300,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>73</v>
       </c>
       <c r="E7">
         <v>94</v>
@@ -1333,10 +1315,10 @@
         <v>28.7</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1344,13 +1326,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>84.8</v>
       </c>
       <c r="E8">
         <v>107.6</v>
@@ -1370,13 +1352,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>95.7</v>
       </c>
       <c r="E9">
         <v>121.1</v>
@@ -1396,13 +1378,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>169.2</v>
       </c>
       <c r="E10">
         <v>212.8</v>
@@ -1422,13 +1404,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>76.1</v>
       </c>
       <c r="E11">
         <v>93.6</v>
@@ -1437,10 +1419,10 @@
         <v>22.9</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1448,13 +1430,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>90.3</v>
       </c>
       <c r="E12">
         <v>106.2</v>
@@ -1474,13 +1456,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>43</v>
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>97.5</v>
       </c>
       <c r="E13">
         <v>114.2</v>
@@ -1500,13 +1482,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>46</v>
+        <v>33</v>
+      </c>
+      <c r="D14">
+        <v>107.1</v>
       </c>
       <c r="E14">
         <v>121.6</v>
@@ -1526,13 +1508,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
+        <v>35</v>
+      </c>
+      <c r="D15">
+        <v>73</v>
       </c>
       <c r="E15">
         <v>81.7</v>
@@ -1541,10 +1523,10 @@
         <v>11.8</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1552,13 +1534,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
+        <v>37</v>
+      </c>
+      <c r="D16">
+        <v>117.3</v>
       </c>
       <c r="E16">
         <v>129.2</v>
@@ -1578,13 +1560,13 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
+        <v>38</v>
+      </c>
+      <c r="D17">
+        <v>111.5</v>
       </c>
       <c r="E17">
         <v>121.9</v>
@@ -1604,13 +1586,13 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="D18">
+        <v>107.6</v>
       </c>
       <c r="E18">
         <v>117.7</v>
@@ -1630,13 +1612,13 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
+        <v>42</v>
+      </c>
+      <c r="D19">
+        <v>103.8</v>
       </c>
       <c r="E19">
         <v>113.3</v>
@@ -1656,13 +1638,13 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
+        <v>43</v>
+      </c>
+      <c r="D20">
+        <v>125.4</v>
       </c>
       <c r="E20">
         <v>134.8</v>
@@ -1682,13 +1664,13 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>64</v>
+        <v>45</v>
+      </c>
+      <c r="D21">
+        <v>117.4</v>
       </c>
       <c r="E21">
         <v>116</v>
@@ -1701,6 +1683,2268 @@
       </c>
       <c r="H21">
         <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>74.3</v>
+      </c>
+      <c r="E22">
+        <v>97.6</v>
+      </c>
+      <c r="F22">
+        <v>31.4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>90.3</v>
+      </c>
+      <c r="E23">
+        <v>113.3</v>
+      </c>
+      <c r="F23">
+        <v>25.4</v>
+      </c>
+      <c r="G23">
+        <v>100.4</v>
+      </c>
+      <c r="H23">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>76.9</v>
+      </c>
+      <c r="E24">
+        <v>95.6</v>
+      </c>
+      <c r="F24">
+        <v>24.3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25">
+        <v>144.8</v>
+      </c>
+      <c r="E25">
+        <v>176.5</v>
+      </c>
+      <c r="F25">
+        <v>21.8</v>
+      </c>
+      <c r="G25">
+        <v>100.4</v>
+      </c>
+      <c r="H25">
+        <v>75.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26">
+        <v>69.2</v>
+      </c>
+      <c r="E26">
+        <v>81.7</v>
+      </c>
+      <c r="F26">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27">
+        <v>107.1</v>
+      </c>
+      <c r="E27">
+        <v>124.8</v>
+      </c>
+      <c r="F27">
+        <v>16.4</v>
+      </c>
+      <c r="G27">
+        <v>100.4</v>
+      </c>
+      <c r="H27">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28">
+        <v>73</v>
+      </c>
+      <c r="E28">
+        <v>84.7</v>
+      </c>
+      <c r="F28">
+        <v>16</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29">
+        <v>95.7</v>
+      </c>
+      <c r="E29">
+        <v>110.9</v>
+      </c>
+      <c r="F29">
+        <v>15.8</v>
+      </c>
+      <c r="G29">
+        <v>100.4</v>
+      </c>
+      <c r="H29">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30">
+        <v>117.3</v>
+      </c>
+      <c r="E30">
+        <v>134.5</v>
+      </c>
+      <c r="F30">
+        <v>14.7</v>
+      </c>
+      <c r="G30">
+        <v>100.4</v>
+      </c>
+      <c r="H30">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31">
+        <v>68.8</v>
+      </c>
+      <c r="E31">
+        <v>77.5</v>
+      </c>
+      <c r="F31">
+        <v>12.6</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32">
+        <v>107.6</v>
+      </c>
+      <c r="E32">
+        <v>119.2</v>
+      </c>
+      <c r="F32">
+        <v>10.7</v>
+      </c>
+      <c r="G32">
+        <v>100.4</v>
+      </c>
+      <c r="H32">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33">
+        <v>84.8</v>
+      </c>
+      <c r="E33">
+        <v>93.8</v>
+      </c>
+      <c r="F33">
+        <v>10.6</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34">
+        <v>111.5</v>
+      </c>
+      <c r="E34">
+        <v>123</v>
+      </c>
+      <c r="F34">
+        <v>10.2</v>
+      </c>
+      <c r="G34">
+        <v>100.4</v>
+      </c>
+      <c r="H34">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35">
+        <v>103.8</v>
+      </c>
+      <c r="E35">
+        <v>114.2</v>
+      </c>
+      <c r="F35">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>100.4</v>
+      </c>
+      <c r="H35">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36">
+        <v>125.4</v>
+      </c>
+      <c r="E36">
+        <v>135</v>
+      </c>
+      <c r="F36">
+        <v>7.6</v>
+      </c>
+      <c r="G36">
+        <v>100.4</v>
+      </c>
+      <c r="H36">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37">
+        <v>111.1</v>
+      </c>
+      <c r="E37">
+        <v>116.3</v>
+      </c>
+      <c r="F37">
+        <v>4.6</v>
+      </c>
+      <c r="G37">
+        <v>100.4</v>
+      </c>
+      <c r="H37">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38">
+        <v>117.4</v>
+      </c>
+      <c r="E38">
+        <v>115.8</v>
+      </c>
+      <c r="F38">
+        <v>-1.3</v>
+      </c>
+      <c r="G38">
+        <v>100.4</v>
+      </c>
+      <c r="H38">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39">
+        <v>169.2</v>
+      </c>
+      <c r="E39">
+        <v>154.6</v>
+      </c>
+      <c r="F39">
+        <v>-8.5</v>
+      </c>
+      <c r="G39">
+        <v>100.4</v>
+      </c>
+      <c r="H39">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40">
+        <v>126.9</v>
+      </c>
+      <c r="E40">
+        <v>115.7</v>
+      </c>
+      <c r="F40">
+        <v>-8.8</v>
+      </c>
+      <c r="G40">
+        <v>100.4</v>
+      </c>
+      <c r="H40">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41">
+        <v>74.3</v>
+      </c>
+      <c r="E41">
+        <v>96.5</v>
+      </c>
+      <c r="F41">
+        <v>29.8</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42">
+        <v>90.3</v>
+      </c>
+      <c r="E42">
+        <v>115.6</v>
+      </c>
+      <c r="F42">
+        <v>27.9</v>
+      </c>
+      <c r="G42">
+        <v>100.6</v>
+      </c>
+      <c r="H42">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43">
+        <v>103.8</v>
+      </c>
+      <c r="E43">
+        <v>127.8</v>
+      </c>
+      <c r="F43">
+        <v>23</v>
+      </c>
+      <c r="G43">
+        <v>100.6</v>
+      </c>
+      <c r="H43">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>76.9</v>
+      </c>
+      <c r="E44">
+        <v>92.4</v>
+      </c>
+      <c r="F44">
+        <v>20.2</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45">
+        <v>144.8</v>
+      </c>
+      <c r="E45">
+        <v>172.4</v>
+      </c>
+      <c r="F45">
+        <v>19</v>
+      </c>
+      <c r="G45">
+        <v>100.6</v>
+      </c>
+      <c r="H45">
+        <v>71.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46">
+        <v>117.3</v>
+      </c>
+      <c r="E46">
+        <v>139.1</v>
+      </c>
+      <c r="F46">
+        <v>18.6</v>
+      </c>
+      <c r="G46">
+        <v>100.6</v>
+      </c>
+      <c r="H46">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47">
+        <v>107.1</v>
+      </c>
+      <c r="E47">
+        <v>126.8</v>
+      </c>
+      <c r="F47">
+        <v>18.3</v>
+      </c>
+      <c r="G47">
+        <v>100.6</v>
+      </c>
+      <c r="H47">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48">
+        <v>73</v>
+      </c>
+      <c r="E48">
+        <v>85.1</v>
+      </c>
+      <c r="F48">
+        <v>16.4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49">
+        <v>69.2</v>
+      </c>
+      <c r="E49">
+        <v>79.3</v>
+      </c>
+      <c r="F49">
+        <v>14.6</v>
+      </c>
+      <c r="G49" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50">
+        <v>95.7</v>
+      </c>
+      <c r="E50">
+        <v>109.4</v>
+      </c>
+      <c r="F50">
+        <v>14.3</v>
+      </c>
+      <c r="G50">
+        <v>100.6</v>
+      </c>
+      <c r="H50">
+        <v>8.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51">
+        <v>73</v>
+      </c>
+      <c r="E51">
+        <v>81.9</v>
+      </c>
+      <c r="F51">
+        <v>12.1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52">
+        <v>107.6</v>
+      </c>
+      <c r="E52">
+        <v>120.8</v>
+      </c>
+      <c r="F52">
+        <v>12.1</v>
+      </c>
+      <c r="G52">
+        <v>100.6</v>
+      </c>
+      <c r="H52">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53">
+        <v>80.7</v>
+      </c>
+      <c r="E53">
+        <v>90.4</v>
+      </c>
+      <c r="F53">
+        <v>11.9</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54">
+        <v>96.7</v>
+      </c>
+      <c r="E54">
+        <v>108.1</v>
+      </c>
+      <c r="F54">
+        <v>11.8</v>
+      </c>
+      <c r="G54">
+        <v>100.6</v>
+      </c>
+      <c r="H54">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55">
+        <v>111.5</v>
+      </c>
+      <c r="E55">
+        <v>121.9</v>
+      </c>
+      <c r="F55">
+        <v>9.3</v>
+      </c>
+      <c r="G55">
+        <v>100.6</v>
+      </c>
+      <c r="H55">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56">
+        <v>125.4</v>
+      </c>
+      <c r="E56">
+        <v>135.4</v>
+      </c>
+      <c r="F56">
+        <v>7.9</v>
+      </c>
+      <c r="G56">
+        <v>100.6</v>
+      </c>
+      <c r="H56">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57">
+        <v>111.1</v>
+      </c>
+      <c r="E57">
+        <v>116.1</v>
+      </c>
+      <c r="F57">
+        <v>4.5</v>
+      </c>
+      <c r="G57">
+        <v>100.6</v>
+      </c>
+      <c r="H57">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" t="s">
+        <v>45</v>
+      </c>
+      <c r="D58">
+        <v>117.4</v>
+      </c>
+      <c r="E58">
+        <v>117.7</v>
+      </c>
+      <c r="F58">
+        <v>0.2</v>
+      </c>
+      <c r="G58">
+        <v>100.6</v>
+      </c>
+      <c r="H58">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59">
+        <v>126.9</v>
+      </c>
+      <c r="E59">
+        <v>116.1</v>
+      </c>
+      <c r="F59">
+        <v>-8.4</v>
+      </c>
+      <c r="G59">
+        <v>100.6</v>
+      </c>
+      <c r="H59">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60">
+        <v>169.2</v>
+      </c>
+      <c r="E60">
+        <v>144.9</v>
+      </c>
+      <c r="F60">
+        <v>-14.3</v>
+      </c>
+      <c r="G60">
+        <v>100.6</v>
+      </c>
+      <c r="H60">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>52</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61">
+        <v>90.3</v>
+      </c>
+      <c r="E61">
+        <v>115.5</v>
+      </c>
+      <c r="F61">
+        <v>27.9</v>
+      </c>
+      <c r="G61">
+        <v>101</v>
+      </c>
+      <c r="H61">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62">
+        <v>74.3</v>
+      </c>
+      <c r="E62">
+        <v>93.5</v>
+      </c>
+      <c r="F62">
+        <v>25.9</v>
+      </c>
+      <c r="G62" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>52</v>
+      </c>
+      <c r="B63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63">
+        <v>117.3</v>
+      </c>
+      <c r="E63">
+        <v>142.5</v>
+      </c>
+      <c r="F63">
+        <v>21.5</v>
+      </c>
+      <c r="G63">
+        <v>101</v>
+      </c>
+      <c r="H63">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64">
+        <v>107.1</v>
+      </c>
+      <c r="E64">
+        <v>129.2</v>
+      </c>
+      <c r="F64">
+        <v>20.6</v>
+      </c>
+      <c r="G64">
+        <v>101</v>
+      </c>
+      <c r="H64">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65">
+        <v>76.9</v>
+      </c>
+      <c r="E65">
+        <v>90.9</v>
+      </c>
+      <c r="F65">
+        <v>18.2</v>
+      </c>
+      <c r="G65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" t="s">
+        <v>42</v>
+      </c>
+      <c r="D66">
+        <v>103.8</v>
+      </c>
+      <c r="E66">
+        <v>121.6</v>
+      </c>
+      <c r="F66">
+        <v>17.1</v>
+      </c>
+      <c r="G66">
+        <v>101</v>
+      </c>
+      <c r="H66">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>52</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67">
+        <v>144.8</v>
+      </c>
+      <c r="E67">
+        <v>168.8</v>
+      </c>
+      <c r="F67">
+        <v>16.5</v>
+      </c>
+      <c r="G67">
+        <v>101</v>
+      </c>
+      <c r="H67">
+        <v>67.1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>52</v>
+      </c>
+      <c r="B68" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" t="s">
+        <v>51</v>
+      </c>
+      <c r="D68">
+        <v>96.7</v>
+      </c>
+      <c r="E68">
+        <v>111</v>
+      </c>
+      <c r="F68">
+        <v>14.8</v>
+      </c>
+      <c r="G68">
+        <v>101</v>
+      </c>
+      <c r="H68">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>52</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69">
+        <v>69.2</v>
+      </c>
+      <c r="E69">
+        <v>79.4</v>
+      </c>
+      <c r="F69">
+        <v>14.7</v>
+      </c>
+      <c r="G69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>52</v>
+      </c>
+      <c r="B70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70">
+        <v>73</v>
+      </c>
+      <c r="E70">
+        <v>83.6</v>
+      </c>
+      <c r="F70">
+        <v>14.5</v>
+      </c>
+      <c r="G70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" t="s">
+        <v>54</v>
+      </c>
+      <c r="D71">
+        <v>68.3</v>
+      </c>
+      <c r="E71">
+        <v>77.1</v>
+      </c>
+      <c r="F71">
+        <v>13</v>
+      </c>
+      <c r="G71" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" t="s">
+        <v>39</v>
+      </c>
+      <c r="C72" t="s">
+        <v>40</v>
+      </c>
+      <c r="D72">
+        <v>107.6</v>
+      </c>
+      <c r="E72">
+        <v>121.6</v>
+      </c>
+      <c r="F72">
+        <v>12.9</v>
+      </c>
+      <c r="G72">
+        <v>101</v>
+      </c>
+      <c r="H72">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73">
+        <v>95.7</v>
+      </c>
+      <c r="E73">
+        <v>108</v>
+      </c>
+      <c r="F73">
+        <v>12.8</v>
+      </c>
+      <c r="G73">
+        <v>101</v>
+      </c>
+      <c r="H73">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>52</v>
+      </c>
+      <c r="B74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" t="s">
+        <v>35</v>
+      </c>
+      <c r="D74">
+        <v>73</v>
+      </c>
+      <c r="E74">
+        <v>82.1</v>
+      </c>
+      <c r="F74">
+        <v>12.4</v>
+      </c>
+      <c r="G74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>52</v>
+      </c>
+      <c r="B75" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" t="s">
+        <v>50</v>
+      </c>
+      <c r="D75">
+        <v>80.7</v>
+      </c>
+      <c r="E75">
+        <v>90.5</v>
+      </c>
+      <c r="F75">
+        <v>12.1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>52</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" t="s">
+        <v>55</v>
+      </c>
+      <c r="D76">
+        <v>85</v>
+      </c>
+      <c r="E76">
+        <v>94.8</v>
+      </c>
+      <c r="F76">
+        <v>11.4</v>
+      </c>
+      <c r="G76" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>52</v>
+      </c>
+      <c r="B77" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" t="s">
+        <v>56</v>
+      </c>
+      <c r="D77">
+        <v>61.5</v>
+      </c>
+      <c r="E77">
+        <v>68.3</v>
+      </c>
+      <c r="F77">
+        <v>11</v>
+      </c>
+      <c r="G77" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>52</v>
+      </c>
+      <c r="B78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C78" t="s">
+        <v>57</v>
+      </c>
+      <c r="D78">
+        <v>96.1</v>
+      </c>
+      <c r="E78">
+        <v>106.4</v>
+      </c>
+      <c r="F78">
+        <v>10.6</v>
+      </c>
+      <c r="G78">
+        <v>101</v>
+      </c>
+      <c r="H78">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>52</v>
+      </c>
+      <c r="B79" t="s">
+        <v>39</v>
+      </c>
+      <c r="C79" t="s">
+        <v>43</v>
+      </c>
+      <c r="D79">
+        <v>125.4</v>
+      </c>
+      <c r="E79">
+        <v>137</v>
+      </c>
+      <c r="F79">
+        <v>9.2</v>
+      </c>
+      <c r="G79">
+        <v>101</v>
+      </c>
+      <c r="H79">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>52</v>
+      </c>
+      <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80">
+        <v>111.5</v>
+      </c>
+      <c r="E80">
+        <v>121.5</v>
+      </c>
+      <c r="F80">
+        <v>8.9</v>
+      </c>
+      <c r="G80">
+        <v>101</v>
+      </c>
+      <c r="H80">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>52</v>
+      </c>
+      <c r="B81" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" t="s">
+        <v>31</v>
+      </c>
+      <c r="D81">
+        <v>111.1</v>
+      </c>
+      <c r="E81">
+        <v>116.9</v>
+      </c>
+      <c r="F81">
+        <v>5.2</v>
+      </c>
+      <c r="G81">
+        <v>101</v>
+      </c>
+      <c r="H81">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>52</v>
+      </c>
+      <c r="B82" t="s">
+        <v>44</v>
+      </c>
+      <c r="C82" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82">
+        <v>117.4</v>
+      </c>
+      <c r="E82">
+        <v>120.5</v>
+      </c>
+      <c r="F82">
+        <v>2.6</v>
+      </c>
+      <c r="G82">
+        <v>101</v>
+      </c>
+      <c r="H82">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>52</v>
+      </c>
+      <c r="B83" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" t="s">
+        <v>47</v>
+      </c>
+      <c r="D83">
+        <v>126.9</v>
+      </c>
+      <c r="E83">
+        <v>117.1</v>
+      </c>
+      <c r="F83">
+        <v>-7.7</v>
+      </c>
+      <c r="G83">
+        <v>101</v>
+      </c>
+      <c r="H83">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>52</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84">
+        <v>169.2</v>
+      </c>
+      <c r="E84">
+        <v>140.7</v>
+      </c>
+      <c r="F84">
+        <v>-16.8</v>
+      </c>
+      <c r="G84">
+        <v>101</v>
+      </c>
+      <c r="H84">
+        <v>39.3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85">
+        <v>90.3</v>
+      </c>
+      <c r="E85">
+        <v>117.7</v>
+      </c>
+      <c r="F85">
+        <v>30.3</v>
+      </c>
+      <c r="G85">
+        <v>100.8</v>
+      </c>
+      <c r="H85">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>58</v>
+      </c>
+      <c r="B86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86">
+        <v>74.3</v>
+      </c>
+      <c r="E86">
+        <v>92</v>
+      </c>
+      <c r="F86">
+        <v>23.8</v>
+      </c>
+      <c r="G86" t="s">
+        <v>13</v>
+      </c>
+      <c r="H86" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>58</v>
+      </c>
+      <c r="B87" t="s">
+        <v>36</v>
+      </c>
+      <c r="C87" t="s">
+        <v>37</v>
+      </c>
+      <c r="D87">
+        <v>117.3</v>
+      </c>
+      <c r="E87">
+        <v>144.9</v>
+      </c>
+      <c r="F87">
+        <v>23.5</v>
+      </c>
+      <c r="G87">
+        <v>100.8</v>
+      </c>
+      <c r="H87">
+        <v>43.7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>58</v>
+      </c>
+      <c r="B88" t="s">
+        <v>32</v>
+      </c>
+      <c r="C88" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88">
+        <v>107.1</v>
+      </c>
+      <c r="E88">
+        <v>129.3</v>
+      </c>
+      <c r="F88">
+        <v>20.6</v>
+      </c>
+      <c r="G88">
+        <v>100.8</v>
+      </c>
+      <c r="H88">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>58</v>
+      </c>
+      <c r="B89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89">
+        <v>76.9</v>
+      </c>
+      <c r="E89">
+        <v>89.7</v>
+      </c>
+      <c r="F89">
+        <v>16.6</v>
+      </c>
+      <c r="G89" t="s">
+        <v>13</v>
+      </c>
+      <c r="H89" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>58</v>
+      </c>
+      <c r="B90" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" t="s">
+        <v>51</v>
+      </c>
+      <c r="D90">
+        <v>96.7</v>
+      </c>
+      <c r="E90">
+        <v>111.9</v>
+      </c>
+      <c r="F90">
+        <v>15.6</v>
+      </c>
+      <c r="G90">
+        <v>100.8</v>
+      </c>
+      <c r="H90">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>58</v>
+      </c>
+      <c r="B91" t="s">
+        <v>53</v>
+      </c>
+      <c r="C91" t="s">
+        <v>54</v>
+      </c>
+      <c r="D91">
+        <v>68.3</v>
+      </c>
+      <c r="E91">
+        <v>78.4</v>
+      </c>
+      <c r="F91">
+        <v>14.8</v>
+      </c>
+      <c r="G91" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>58</v>
+      </c>
+      <c r="B92" t="s">
+        <v>22</v>
+      </c>
+      <c r="C92" t="s">
+        <v>49</v>
+      </c>
+      <c r="D92">
+        <v>73</v>
+      </c>
+      <c r="E92">
+        <v>83.8</v>
+      </c>
+      <c r="F92">
+        <v>14.7</v>
+      </c>
+      <c r="G92" t="s">
+        <v>13</v>
+      </c>
+      <c r="H92" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>58</v>
+      </c>
+      <c r="B93" t="s">
+        <v>34</v>
+      </c>
+      <c r="C93" t="s">
+        <v>35</v>
+      </c>
+      <c r="D93">
+        <v>73</v>
+      </c>
+      <c r="E93">
+        <v>83.4</v>
+      </c>
+      <c r="F93">
+        <v>14.2</v>
+      </c>
+      <c r="G93" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>58</v>
+      </c>
+      <c r="B94" t="s">
+        <v>41</v>
+      </c>
+      <c r="C94" t="s">
+        <v>42</v>
+      </c>
+      <c r="D94">
+        <v>103.8</v>
+      </c>
+      <c r="E94">
+        <v>118.4</v>
+      </c>
+      <c r="F94">
+        <v>14</v>
+      </c>
+      <c r="G94">
+        <v>100.8</v>
+      </c>
+      <c r="H94">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>58</v>
+      </c>
+      <c r="B95" t="s">
+        <v>39</v>
+      </c>
+      <c r="C95" t="s">
+        <v>40</v>
+      </c>
+      <c r="D95">
+        <v>107.6</v>
+      </c>
+      <c r="E95">
+        <v>122.6</v>
+      </c>
+      <c r="F95">
+        <v>13.8</v>
+      </c>
+      <c r="G95">
+        <v>100.8</v>
+      </c>
+      <c r="H95">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>58</v>
+      </c>
+      <c r="B96" t="s">
+        <v>28</v>
+      </c>
+      <c r="C96" t="s">
+        <v>50</v>
+      </c>
+      <c r="D96">
+        <v>80.7</v>
+      </c>
+      <c r="E96">
+        <v>91.7</v>
+      </c>
+      <c r="F96">
+        <v>13.5</v>
+      </c>
+      <c r="G96" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>58</v>
+      </c>
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97">
+        <v>69.2</v>
+      </c>
+      <c r="E97">
+        <v>78.6</v>
+      </c>
+      <c r="F97">
+        <v>13.5</v>
+      </c>
+      <c r="G97" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>58</v>
+      </c>
+      <c r="B98" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" t="s">
+        <v>55</v>
+      </c>
+      <c r="D98">
+        <v>85</v>
+      </c>
+      <c r="E98">
+        <v>96.4</v>
+      </c>
+      <c r="F98">
+        <v>13.4</v>
+      </c>
+      <c r="G98" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>58</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99">
+        <v>144.8</v>
+      </c>
+      <c r="E99">
+        <v>163.1</v>
+      </c>
+      <c r="F99">
+        <v>12.5</v>
+      </c>
+      <c r="G99">
+        <v>100.8</v>
+      </c>
+      <c r="H99">
+        <v>61.8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>58</v>
+      </c>
+      <c r="B100" t="s">
+        <v>22</v>
+      </c>
+      <c r="C100" t="s">
+        <v>23</v>
+      </c>
+      <c r="D100">
+        <v>95.7</v>
+      </c>
+      <c r="E100">
+        <v>106.3</v>
+      </c>
+      <c r="F100">
+        <v>10.9</v>
+      </c>
+      <c r="G100">
+        <v>100.8</v>
+      </c>
+      <c r="H100">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>58</v>
+      </c>
+      <c r="B101" t="s">
+        <v>39</v>
+      </c>
+      <c r="C101" t="s">
+        <v>57</v>
+      </c>
+      <c r="D101">
+        <v>96.1</v>
+      </c>
+      <c r="E101">
+        <v>106.5</v>
+      </c>
+      <c r="F101">
+        <v>10.8</v>
+      </c>
+      <c r="G101">
+        <v>100.8</v>
+      </c>
+      <c r="H101">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>58</v>
+      </c>
+      <c r="B102" t="s">
+        <v>44</v>
+      </c>
+      <c r="C102" t="s">
+        <v>56</v>
+      </c>
+      <c r="D102">
+        <v>61.5</v>
+      </c>
+      <c r="E102">
+        <v>67.7</v>
+      </c>
+      <c r="F102">
+        <v>10.1</v>
+      </c>
+      <c r="G102" t="s">
+        <v>13</v>
+      </c>
+      <c r="H102" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>58</v>
+      </c>
+      <c r="B103" t="s">
+        <v>20</v>
+      </c>
+      <c r="C103" t="s">
+        <v>38</v>
+      </c>
+      <c r="D103">
+        <v>111.5</v>
+      </c>
+      <c r="E103">
+        <v>121.6</v>
+      </c>
+      <c r="F103">
+        <v>9</v>
+      </c>
+      <c r="G103">
+        <v>100.8</v>
+      </c>
+      <c r="H103">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>58</v>
+      </c>
+      <c r="B104" t="s">
+        <v>39</v>
+      </c>
+      <c r="C104" t="s">
+        <v>43</v>
+      </c>
+      <c r="D104">
+        <v>125.4</v>
+      </c>
+      <c r="E104">
+        <v>135.7</v>
+      </c>
+      <c r="F104">
+        <v>8.2</v>
+      </c>
+      <c r="G104">
+        <v>100.8</v>
+      </c>
+      <c r="H104">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>58</v>
+      </c>
+      <c r="B105" t="s">
+        <v>30</v>
+      </c>
+      <c r="C105" t="s">
+        <v>31</v>
+      </c>
+      <c r="D105">
+        <v>111.1</v>
+      </c>
+      <c r="E105">
+        <v>116.4</v>
+      </c>
+      <c r="F105">
+        <v>4.8</v>
+      </c>
+      <c r="G105">
+        <v>100.8</v>
+      </c>
+      <c r="H105">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>58</v>
+      </c>
+      <c r="B106" t="s">
+        <v>44</v>
+      </c>
+      <c r="C106" t="s">
+        <v>45</v>
+      </c>
+      <c r="D106">
+        <v>117.4</v>
+      </c>
+      <c r="E106">
+        <v>121.5</v>
+      </c>
+      <c r="F106">
+        <v>3.5</v>
+      </c>
+      <c r="G106">
+        <v>100.8</v>
+      </c>
+      <c r="H106">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>58</v>
+      </c>
+      <c r="B107" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107" t="s">
+        <v>47</v>
+      </c>
+      <c r="D107">
+        <v>126.9</v>
+      </c>
+      <c r="E107">
+        <v>117.3</v>
+      </c>
+      <c r="F107">
+        <v>-7.5</v>
+      </c>
+      <c r="G107">
+        <v>100.8</v>
+      </c>
+      <c r="H107">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>58</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>25</v>
+      </c>
+      <c r="D108">
+        <v>169.2</v>
+      </c>
+      <c r="E108">
+        <v>139.7</v>
+      </c>
+      <c r="F108">
+        <v>-17.4</v>
+      </c>
+      <c r="G108">
+        <v>100.8</v>
+      </c>
+      <c r="H108">
+        <v>38.6</v>
       </c>
     </row>
   </sheetData>

--- a/source/8、绩效异常岗位/7、扫描岗/扫描岗-6月.xlsx
+++ b/source/8、绩效异常岗位/7、扫描岗/扫描岗-6月.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I377"/>
+  <dimension ref="A1:I474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14791,6 +14791,3647 @@
         <v>33.3</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F378" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="G378" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="F379" t="n">
+        <v>148</v>
+      </c>
+      <c r="G379" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H379" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I379" t="n">
+        <v>52.6</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F380" t="n">
+        <v>114</v>
+      </c>
+      <c r="G380" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H380" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I380" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>83</v>
+      </c>
+      <c r="F381" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="G381" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H381" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>荆州</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>73</v>
+      </c>
+      <c r="F382" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="G382" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>邢邯</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="F383" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="G383" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F384" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="G384" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H384" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I384" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="F385" t="n">
+        <v>127</v>
+      </c>
+      <c r="G385" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H385" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I385" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F386" t="n">
+        <v>109</v>
+      </c>
+      <c r="G386" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H386" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I386" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="F387" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="G387" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H387" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I387" t="n">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F388" t="n">
+        <v>113</v>
+      </c>
+      <c r="G388" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H388" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I388" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="F389" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="G389" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="H389" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I389" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="F390" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="G390" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="H390" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I390" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="F391" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="G391" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="H391" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I391" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>重庆区</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="F392" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="G392" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H392" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I392" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="F393" t="n">
+        <v>112</v>
+      </c>
+      <c r="G393" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="H393" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I393" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F394" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="G394" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="H394" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="I394" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="F395" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="G395" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H395" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I395" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F396" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="G396" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H396" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I396" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F397" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="G397" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>83</v>
+      </c>
+      <c r="F398" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="G398" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H398" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>荆州</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>73</v>
+      </c>
+      <c r="F399" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="G399" t="n">
+        <v>14</v>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F400" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="G400" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H400" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I400" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="F401" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="G401" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H401" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I401" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F402" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="G402" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H402" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I402" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="F403" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="G403" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H403" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I403" t="n">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F404" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="G404" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H404" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I404" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="F405" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="G405" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="H405" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I405" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="F406" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="G406" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="H406" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I406" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>重庆区</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="F407" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="G407" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H407" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I407" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="F408" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="G408" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H408" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I408" t="n">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="F409" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="G409" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="H409" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I409" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F410" t="n">
+        <v>128</v>
+      </c>
+      <c r="G410" t="n">
+        <v>-24.3</v>
+      </c>
+      <c r="H410" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I410" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="F411" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="G411" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H411" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I411" t="n">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F412" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="G412" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F413" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="G413" t="n">
+        <v>18</v>
+      </c>
+      <c r="H413" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I413" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>83</v>
+      </c>
+      <c r="F414" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="G414" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H414" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I414" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>荆州</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>73</v>
+      </c>
+      <c r="F415" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="G415" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F416" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="G416" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H416" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I416" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="F417" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="G417" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H417" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I417" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F418" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="G418" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H418" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I418" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="F419" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="G419" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H419" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I419" t="n">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F420" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="G420" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H420" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I420" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="F421" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="G421" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H421" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I421" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="F422" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G422" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H422" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I422" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>重庆区</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="F423" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="G423" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H423" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I423" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="F424" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="G424" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H424" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I424" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="F425" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="G425" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="H425" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I425" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F426" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="G426" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="H426" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I426" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="F427" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="G427" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H427" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I427" t="n">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F428" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="G428" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F429" t="n">
+        <v>111</v>
+      </c>
+      <c r="G429" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H429" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I429" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>83</v>
+      </c>
+      <c r="F430" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G430" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H430" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I430" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>荆州</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>73</v>
+      </c>
+      <c r="F431" t="n">
+        <v>83</v>
+      </c>
+      <c r="G431" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F432" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="G432" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H432" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I432" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="F433" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="G433" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H433" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I433" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F434" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="G434" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H434" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I434" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="F435" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="G435" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H435" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I435" t="n">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F436" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="G436" t="n">
+        <v>0</v>
+      </c>
+      <c r="H436" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I436" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="F437" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="G437" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="H437" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I437" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="F438" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="G438" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="H438" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I438" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>重庆区</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="F439" t="n">
+        <v>107</v>
+      </c>
+      <c r="G439" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H439" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I439" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="F440" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="G440" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="H440" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I440" t="n">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="F441" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="G441" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="H441" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I441" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F442" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="G442" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="H442" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="I442" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F443" t="n">
+        <v>55</v>
+      </c>
+      <c r="G443" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F444" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="G444" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="H444" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I444" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>83</v>
+      </c>
+      <c r="F445" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="G445" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H445" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I445" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>荆州</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>73</v>
+      </c>
+      <c r="F446" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="G446" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F447" t="n">
+        <v>118</v>
+      </c>
+      <c r="G447" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H447" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I447" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="F448" t="n">
+        <v>125</v>
+      </c>
+      <c r="G448" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H448" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I448" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F449" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="G449" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H449" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I449" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="F450" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="G450" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H450" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I450" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F451" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="G451" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H451" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I451" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="F452" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="G452" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H452" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I452" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="F453" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="G453" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="H453" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I453" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>重庆区</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="F454" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G454" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="H454" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I454" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="F455" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="G455" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="H455" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I455" t="n">
+        <v>39.2</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="F456" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="G456" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="H456" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I456" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F457" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="G457" t="n">
+        <v>-25.2</v>
+      </c>
+      <c r="H457" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I457" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>205.8</v>
+      </c>
+      <c r="F458" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="G458" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="H458" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I458" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F459" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="G459" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F460" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="G460" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H460" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I460" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>83</v>
+      </c>
+      <c r="F461" t="n">
+        <v>96</v>
+      </c>
+      <c r="G461" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H461" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I461" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>荆州</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>73</v>
+      </c>
+      <c r="F462" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="G462" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F463" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="G463" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H463" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I463" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="F464" t="n">
+        <v>124.3</v>
+      </c>
+      <c r="G464" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H464" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I464" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F465" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="G465" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H465" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I465" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="F466" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="G466" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H466" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I466" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F467" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="G467" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H467" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I467" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="F468" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="G468" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="H468" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I468" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="F469" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="G469" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="H469" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I469" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>重庆区</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="F470" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="G470" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H470" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I470" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="F471" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="G471" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="H471" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I471" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="F472" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="G472" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="H472" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I472" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F473" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="G473" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="H473" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I473" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>扫描岗</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>205.8</v>
+      </c>
+      <c r="F474" t="n">
+        <v>147.1</v>
+      </c>
+      <c r="G474" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="H474" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="I474" t="n">
+        <v>53.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
